--- a/output/第10期計画_見える化の指標（B5・B6・D49）の受領点検.xlsx
+++ b/output/第10期計画_見える化の指標（B5・B6・D49）の受領点検.xlsx
@@ -5106,8 +5106,8 @@
     <row r="14" ht="70" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>・資料提供依頼は全23件で、なおお待ちしているものが15件です（うち入手先が受託者であるものが1件）。
-・外部にお願いするもの14件のうち、国の告示・公表を待つものが2件（第10期の政令改正・令和7年国勢調査）です。
+          <t>・資料提供依頼は全25件で、なおお待ちしているものが17件です（うち入手先が受託者であるものが1件）。
+・外部にお願いするもの16件のうち、国の告示・公表を待つものが2件（第10期の政令改正・令和7年国勢調査）です。
 ・今回の受領により、入手先を見える化システムとしていた2件がいずれも受領済となりました。</t>
         </is>
       </c>

--- a/output/第10期計画_見える化の指標（B5・B6・D49）の受領点検.xlsx
+++ b/output/第10期計画_見える化の指標（B5・B6・D49）の受領点検.xlsx
@@ -1405,12 +1405,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>No.1〜No.190</t>
+          <t>No.1〜No.192</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>190件</t>
+          <t>192件</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -5106,8 +5106,8 @@
     <row r="14" ht="70" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>・資料提供依頼は全25件で、なおお待ちしているものが17件です（うち入手先が受託者であるものが1件）。
-・外部にお願いするもの16件のうち、国の告示・公表を待つものが2件（第10期の政令改正・令和7年国勢調査）です。
+          <t>・資料提供依頼は全30件で、なおお待ちしているものが22件です（うち入手先が受託者であるものが1件）。
+・外部にお願いするもの21件のうち、国の告示・公表を待つものが2件（第10期の政令改正・令和7年国勢調査）です。
 ・今回の受領により、入手先を見える化システムとしていた2件がいずれも受領済となりました。</t>
         </is>
       </c>
